--- a/tables/Alcohol_Tier2_Qualitative.xlsx
+++ b/tables/Alcohol_Tier2_Qualitative.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,14 +523,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dusen 1967</t>
+          <t>Smart 1966</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="C3" t="n">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -539,17 +539,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Group means (Tx vs Ctrl)</t>
+          <t>Non-significant 3-group ANOVA (multi-df F) — percentage gain in abstinence</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.97 vs 4.03</t>
+          <t>34 vs 32 vs 20 (%, lysergide vs ephedrine vs control)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Group means without SDs; ns</t>
+          <t>Two-group proportions; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Group means virtually identical (3.97 vs 4.03); reported non-significant.</t>
+          <t>Non-significant omnibus test across lysergide/ephedrine/control on the abstract-leading abstinence-gain outcome; lysergide had the numerically largest gain (~34%) but was statistically indistinguishable from the active ephedrine comparator (~32%) and not clearly superior to the no-drug control (~20%), and every other reported drinking-behavior outcome (drinking occasions, drunkenness occasions, symptom checklist, clinic contacts) was also non-significant between groups — the authors' own conclusion is that lysergide 'failed as an effective adjunct to psychotherapy.'</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -572,15 +572,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Johnson 1969</t>
+          <t>Dusen 1967</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1969</v>
-      </c>
-      <c r="C4" t="n">
-        <v>95</v>
-      </c>
+        <v>1967</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>LSD</t>
@@ -591,10 +589,14 @@
           <t>Non-significant (no statistic)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4.03 vs 3.97 (18-month mean outcome score, 2=worse...5=much improved scale; prelysergide control N=37 vs Lysergide Experiment N=56)</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Reported only as "NS"</t>
+          <t>Group means without SDs; ns</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -609,7 +611,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Reported only as non-significant; no test statistic given.</t>
+          <t>The lysergide-experiment group's 18-month mean (3.97) is numerically lower than the prelysergide historical-control group's (4.03), and the article states differences across all groups 'did not even approach significance' by chi-square and Duncan's range test; the study's own conclusion is that lysergide 'did not increase the patients' abstinence.'</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -617,25 +619,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Denson 1970</t>
+          <t>Johnson 1969</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1970</v>
-      </c>
-      <c r="C5" t="n">
-        <v>51</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>LSD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Non-significant (no statistic)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No outcome statistic reported</t>
+          <t>Reported only as "NS"</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -650,7 +654,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Authors say: results obtained from statistical analysis of the data were interpreted as negative.</t>
+          <t>All four arms (two LSD arms, an active-drug control, and a no-drug routine-care control) showed statistically significant pre-to-post improvement on drinking indices (p&lt;.01 to p&lt;.10), but the ANOVA between-groups test was non-significant on every criterion in Table 4, and the authors explicitly conclude LSD conferred no advantage over the comparator conditions -- a null differential-effect result rather than a negative one.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -658,80 +662,82 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Thurgur 2025</t>
+          <t>Pahnke 1970</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2025</v>
+        <v>1970</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MDMA</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bayesian posterior probability</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.63</v>
+          <t>Two-group proportions (%)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>53 vs 33</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bayesian posterior not directly convertible</t>
+          <t>Two dose-group proportions; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>moderate_positive</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Null / NS</t>
+          <t>Moderate Positive (OR 1.5-3 or g 0.5-0.8)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bayesian posterior P(positive effect)=0.63; insufficient evidence above chance threshold (flat prior).</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Computed OR=2.29 from two-group abstinence proportions (53% vs 33%); falls in OR 1.5-3 range.</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2.29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Smart 1966</t>
+          <t>Grabski 2022</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1966</v>
+        <v>2022</v>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>33.7 vs 19.6</t>
-        </is>
+          <t>Mean difference (percentage days abstinent, %), site-adjusted intention-to-treat, ketamine vs. placebo pooled across therapy conditions at 6 months</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>10.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Two-group proportions; downgrade to Tier 2</t>
+          <t>Mean difference reported without SDs</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -746,43 +752,37 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Computed OR=2.08 from two-group abstinence proportions (33.7% vs 19.6%); falls in OR 1.5-3 range.</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2.08</v>
-      </c>
+          <t>Significant ITT mean difference of 10.1 percentage points (95% CI 1.1, 19.0) in percentage days abstinent at 6 months, ketamine vs. placebo pooled across therapy arms, in a 4-arm double-blind RCT (N=89 analyzed at this timepoint); the co-primary relapse outcome was null (OR=0.70, 95% CI 0.28-1.75).</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pahnke 1970</t>
+          <t>Pagni 2024</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1970</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="n">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Psilocybin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>53 vs 33</t>
-        </is>
-      </c>
+          <t>Whole-brain fMRI cluster-level statistics (multiple discrete clusters comprising the primary outcome; no single scalar effect size)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Two dose-group proportions; downgrade to Tier 2</t>
+          <t>Within-subjects t (df=3); not between-groups</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -797,90 +797,90 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Computed OR=2.29 from two-group abstinence proportions (53% vs 33%); falls in OR 1.5-3 range.</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2.29</v>
-      </c>
+          <t>Significant reduction in psilocybin-group cue-elicited craving post-treatment (t(3)=5.568, p=0.0114) plus multiple significant whole-brain treatment-by-time interaction clusters in the direction the authors interpret as therapeutic (increased PFC/caudate engagement, decreased insula/motor/cerebellar activity), tempered by the very small pilot sample (n=11), uncorrected p&lt;.005 whole-brain threshold, and the authors' own caution that some directionality is not straightforwardly consistent with AUD-circuit normalization.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grabski 2022</t>
+          <t>Jensen 1963</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2022</v>
+        <v>1963</v>
       </c>
       <c r="C9" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mean difference (%)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>10.1</v>
+          <t>Two-group proportions (%)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>63 vs 27</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mean difference reported without SDs</t>
+          <t>Two-group proportions; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>moderate_positive</t>
+          <t>large_positive</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Moderate Positive (OR 1.5-3 or g 0.5-0.8)</t>
+          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+10.1 percentage-point difference in heavy drinking days favoring ketamine; no SD reported so Tier 1 conversion not feasible.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>Computed OR=4.60 from two-group abstinence proportions (63% vs 27%); exceeds OR≥3 threshold.</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jensen 1963</t>
+          <t>Heinzerling 2023</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1963</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Psilocybin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>63 vs 27</t>
-        </is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>15.76</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Two-group proportions; downgrade to Tier 2</t>
+          <t>F has 6 df numerator; repeated-measures design</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -895,56 +895,56 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Computed OR=4.60 from two-group abstinence proportions (63% vs 27%); exceeds OR≥3 threshold.</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4.6</v>
-      </c>
+          <t>F(6,df)=15.76 for time-by-treatment interaction, p&lt;0.001; repeated-measures design with sustained treatment advantage.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Heinzerling 2023</t>
+          <t>Smith 1958</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
+        <v>1958</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Psilocybin</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>15.76</v>
+          <t>Single-arm improvement rate (%)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>12/24 (50%)</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>F has 6 df numerator; repeated-measures design</t>
+          <t>Single-arm improvement rate</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>large_positive</t>
+          <t>single_arm_positive</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
+          <t>Positive (Single-arm, no comparator)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>F(6,df)=15.76 for time-by-treatment interaction, p&lt;0.001; repeated-measures design with sustained treatment advantage.</t>
+          <t>50% of a deliberately refractory, A.A.-failure alcoholic sample (12/24) were rated much improved or improved on drinking outcome post-treatment, none worsened, and the authors characterize the results as sufficiently encouraging to justify further controlled trials.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -952,46 +952,48 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gent 2024</t>
+          <t>MacLean 1961</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>1961</v>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>6.45</v>
+          <t>Single-arm improvement rate (%)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>46/61 (75.4%)</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>F has 2 df numerator (3-arm); not 1-df comparison</t>
+          <t>Single-arm improvement rate</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>large_positive</t>
+          <t>single_arm_positive</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
+          <t>Positive (Single-arm, no comparator)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>F(2,df)=6.45, p&lt;0.01 in 3-arm RCT; overall ANOVA significant, favoring active treatment over placebo.</t>
+          <t>75.4% (46/61) of the alcoholic subgroup was rated much improved or improved on the composite outcome (which for alcoholics required abstinence or a definite reduction in drinking versus the prior 12 months), a directionally positive single-arm result with no control group.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -999,14 +1001,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Smith 1958</t>
+          <t>O'Reilly 1964</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1958</v>
+        <v>1964</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1015,15 +1017,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Improvement rate (%)</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>50</v>
+          <t>Abstinence rate (%)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>38% (26/68)</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Single-arm improvement rate</t>
+          <t>Single-arm abstinence rate</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1038,7 +1042,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>50% improvement rate (12/24 patients); single-arm study with no comparator.</t>
+          <t>38% abstinence (26/68) at follow-up (mean 14 months post-treatment), explicitly framed by the authors as having 'produced sobriety... without any disastrous side effects' — a positive pre/post result in a single-arm design.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1046,14 +1050,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MacLean 1961</t>
+          <t>Kurland 1967</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1961</v>
+        <v>1967</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1062,15 +1066,13 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Improvement rate (%)</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>49</v>
-      </c>
+          <t>Abstinence rate (%), single-arm</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Single-arm improvement rate</t>
+          <t>Single-arm rate; no comparator</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1085,7 +1087,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>49% improvement rate; single-arm open-label study with no comparator.</t>
+          <t>23/69 (33%) maintained abstinence at 6-month follow-up in a single-arm, open-label pilot; MMPI clinical-scale changes reported as significant and in a positive direction; authors state 'no patient has been harmed' and describe benefit as 'considerable' in some cases.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1093,31 +1095,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O'Reilly 1964</t>
+          <t>Sessa 2019</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1964</v>
+        <v>2019</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>MDMA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Abstinence rate (%)</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>38</v>
+          <t>Single-arm rate (no inferential statistic)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4/4 (100%) tolerated; 2/4 alcohol-free, 2/4 single low-dose lapse only</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Single-arm abstinence rate</t>
+          <t>Case series 2/4 abstinent; no comparator</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1132,7 +1136,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38% abstinence rate; single-arm study with no comparator group.</t>
+          <t>All 4 participants avoided harmful/daily drinking post-treatment (2 fully alcohol-free, 2 with only a single low-dose lapse), no serious adverse events, and improvement on GAD-7, PHQ-9, SF-36 and SCS — a favorable single-arm pre/post pattern with no comparator.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1140,31 +1144,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kurland 1967</t>
+          <t>Yoon 2019</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1967</v>
+        <v>2019</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Abstinence rate (%)</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>33.3</v>
-      </c>
+          <t>Single-arm response rate (%)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Single-arm rate; no comparator</t>
+          <t>Case series 5/5 response; no comparator</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1179,7 +1181,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33.3% abstinence rate at follow-up; single-arm study with no comparator group.</t>
+          <t>100% (5/5) met the pre-specified clinical response criterion by the fourth ketamine infusion, and 80% (4/5) reported improved alcohol craving/consumption on the OCDS, in a single-arm open-label design with no comparator.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1187,14 +1189,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sessa 2019</t>
+          <t>Sessa 2021</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1203,15 +1205,13 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Abstinence rate (%)</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>50</v>
-      </c>
+          <t>Descriptive completion/safety rate (no inferential statistic)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Case series 2/4 abstinent; no comparator</t>
+          <t>Within-group mean change; no comparator</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>50% abstinence rate (2/4); case series with no comparator.</t>
+          <t>Single-arm design with a favourable within-subject direction on both the primary outcome (85.7% completed both MDMA sessions, no unexpected AEs) and the secondary outcome (alcohol consumption fell from 130.6 to 18.7 units/week at 9-month follow-up; 9/14 totally abstinent).</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1234,14 +1234,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Yoon 2019</t>
+          <t>Marvania 2024</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1250,15 +1250,13 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Response rate (%)</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>100</v>
-      </c>
+          <t>Paired t-test (within-subjects, no comparator arm)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Case series 5/5 response; no comparator</t>
+          <t>Within-group AASE change; no comparator</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1273,7 +1271,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>100% response rate (5/5); case series with no comparator.</t>
+          <t>Statistically significant within-subject increase in AASE confidence-to-abstain score sustained from baseline to 2-week post-treatment follow-up (51.98% increase, T=-4.982, p&lt;0.05), in a single-arm study with no comparator group.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1281,11 +1279,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sessa 2021</t>
+          <t>Thurgur 2025</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C19" t="n">
         <v>14</v>
@@ -1297,17 +1295,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Within-group mean change</t>
+          <t>Bayesian posterior probability (single-arm binomial success rate)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18.7 vs 130.6</t>
+          <t>9/14 (Bayesian posterior probability of treatment success: 0.63 flat prior, 0.55 skeptical prior)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Within-group mean change; no comparator</t>
+          <t>Bayesian posterior not directly convertible</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1322,104 +1320,10 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Within-group reduction from 130.6 to 18.7 units/wk at 9 months; no comparator arm.</t>
+          <t>Single-arm, open-label secondary analysis; 9/14 (64%) participants achieved the pre-defined 2-level WHO drinking-risk reduction success threshold, with Bayesian posterior probability of success 55-63% depending on prior, and multiple secondary craving/sleep/self-compassion PROMs improved significantly at 3 months -- directionally positive though the preliminary frequentist binomial test against a 50% null was not significant (P=.423).</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Marvania 2024</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C20" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Ketamine</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Within-group change (%)</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>51.98</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Within-group AASE change; no comparator</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>single_arm_positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Positive (Single-arm, no comparator)</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>51.98% within-group improvement on AASE scale; no comparator arm.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pagni 2024</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C21" t="n">
-        <v>11</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Psilocybin</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>5.568</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Within-subjects t (df=3); not between-groups</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>single_arm_positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Positive (Single-arm, no comparator)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Within-subjects t(3)=5.568, p&lt;0.05 for craving reduction on fMRI; N=4, within-subjects design, no comparator arm.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/Alcohol_Tier2_Qualitative.xlsx
+++ b/tables/Alcohol_Tier2_Qualitative.xlsx
@@ -578,7 +578,9 @@
       <c r="B4" t="n">
         <v>1967</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>99</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>LSD</t>
@@ -625,7 +627,9 @@
       <c r="B5" t="n">
         <v>1969</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>95</v>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>LSD</t>
@@ -720,7 +724,7 @@
         <v>2022</v>
       </c>
       <c r="C7" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
